--- a/Machine Learning/PII/Research_Proposal/Deepak_Goyal_Research+Proposal+Call+3+Checklist.xlsx
+++ b/Machine Learning/PII/Research_Proposal/Deepak_Goyal_Research+Proposal+Call+3+Checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\Machine Learning\PII\Research_Proposal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{403975CC-6708-4DE9-81D1-6D0B227C4AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132B6CEE-4A83-4F24-862F-27F47EB2DEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -258,12 +258,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,7 +510,7 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -524,7 +524,7 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="12"/>
+      <c r="A3" s="13"/>
       <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
@@ -536,7 +536,7 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="12"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
@@ -548,7 +548,7 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
@@ -560,7 +560,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="9" t="s">
         <v>12</v>
       </c>
@@ -572,7 +572,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="9" t="s">
         <v>13</v>
       </c>
@@ -584,7 +584,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="13"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="9" t="s">
         <v>14</v>
       </c>
@@ -747,19 +747,19 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.2" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="11">
         <v>45883</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="11">
         <v>45879</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -767,17 +767,17 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="54.6" customHeight="1">
-      <c r="A3" s="12"/>
+      <c r="A3" s="13"/>
       <c r="B3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="11">
         <v>45883</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="11">
         <v>45879</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -785,17 +785,17 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="49.8" customHeight="1">
-      <c r="A4" s="12"/>
+      <c r="A4" s="13"/>
       <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="11">
         <v>45883</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <v>45879</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -803,17 +803,17 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="49.2" customHeight="1">
-      <c r="A5" s="12"/>
+      <c r="A5" s="13"/>
       <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="11">
         <v>45883</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="11">
         <v>45879</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -821,17 +821,17 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="32.4" customHeight="1">
-      <c r="A6" s="12"/>
+      <c r="A6" s="13"/>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="11">
         <v>45883</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="11">
         <v>45879</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -839,17 +839,17 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="33.6" customHeight="1">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="11">
         <v>45883</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="11">
         <v>45879</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -857,17 +857,17 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="51.6" customHeight="1">
-      <c r="A8" s="13"/>
+      <c r="A8" s="14"/>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="11">
         <v>45883</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="11">
         <v>45879</v>
       </c>
       <c r="F8" s="4" t="s">
